--- a/Analise-Critica/Analise-Critica-modelo.xlsx
+++ b/Analise-Critica/Analise-Critica-modelo.xlsx
@@ -1156,7 +1156,7 @@
     <t xml:space="preserve">O sistema cobre bem o delivery, e pouco o restante da loja.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dois registros no ano, os dois da auditoria 2026-03. O RNC 2026-05 foi encerrado como eficaz. O segundo está em verificação.</t>
+    <t xml:space="preserve">Três registros abertos pela auditoria 2026-03. O RNC 2026-05 foi encerrado como eficaz. Os outros dois estão em verificação.</t>
   </si>
   <si>
     <t xml:space="preserve">O tratamento funciona. Manter.</t>
@@ -1171,7 +1171,7 @@
     <t xml:space="preserve">As medições são feitas e usadas. Manter.</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma auditoria no ano, no delivery: duas não conformidades menores e uma oportunidade de melhoria. O salão e as compras nunca foram auditados.</t>
+    <t xml:space="preserve">A auditoria 2026-03, no delivery: três não conformidades menores. O salão e as compras nunca foram auditados.</t>
   </si>
   <si>
     <t xml:space="preserve">O programa de auditoria precisa cobrir os outros processos.</t>
@@ -2194,11 +2194,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="66066051"/>
-        <c:axId val="34742486"/>
+        <c:axId val="96490303"/>
+        <c:axId val="35167514"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66066051"/>
+        <c:axId val="96490303"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2230,7 +2230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34742486"/>
+        <c:crossAx val="35167514"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2238,7 +2238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34742486"/>
+        <c:axId val="35167514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2278,7 +2278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66066051"/>
+        <c:crossAx val="96490303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2420,11 +2420,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="33181274"/>
-        <c:axId val="96108305"/>
+        <c:axId val="50633389"/>
+        <c:axId val="46297849"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33181274"/>
+        <c:axId val="50633389"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96108305"/>
+        <c:crossAx val="46297849"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2464,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96108305"/>
+        <c:axId val="46297849"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2504,7 +2504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33181274"/>
+        <c:crossAx val="50633389"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5430,16 +5430,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H21" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Item da entrada: a, b, c1 a c7, d, e ou f" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C21" type="list">
       <formula1>"a,b,c1,c2,c3,c4,c5,c6,c7,d,e,f"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Melhoria, Mudança no sistema ou Recursos" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E7:E21" type="list">
       <formula1>"Melhoria,Mudança no sistema,Recursos"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H21" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J7:J21" type="decimal">

--- a/Analise-Critica/Analise-Critica-modelo.xlsx
+++ b/Analise-Critica/Analise-Critica-modelo.xlsx
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">Gerente da loja</t>
   </si>
   <si>
-    <t xml:space="preserve">Primeira análise crítica: não há ações anteriores. O ponto de partida é o diagnóstico, com 68% de atendimento.</t>
+    <t xml:space="preserve">Primeira análise crítica: não há ações anteriores. O ponto de partida é o diagnóstico, com 67% de atendimento.</t>
   </si>
   <si>
     <t xml:space="preserve">Sem histórico</t>
@@ -1357,7 +1357,7 @@
     <t xml:space="preserve">Gerente de engenharia</t>
   </si>
   <si>
-    <t xml:space="preserve">Instalar o medidor de espessura em linha na extrusora 3.</t>
+    <t xml:space="preserve">Orçar os medidores de espessura em linha para as extrusoras 3 e 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Orçamento recebido. Compra não aprovada.</t>
@@ -2194,11 +2194,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="96490303"/>
-        <c:axId val="35167514"/>
+        <c:axId val="48465311"/>
+        <c:axId val="80558773"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96490303"/>
+        <c:axId val="48465311"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2230,7 +2230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35167514"/>
+        <c:crossAx val="80558773"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2238,7 +2238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35167514"/>
+        <c:axId val="80558773"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2278,7 +2278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96490303"/>
+        <c:crossAx val="48465311"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2420,11 +2420,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="50633389"/>
-        <c:axId val="46297849"/>
+        <c:axId val="37551409"/>
+        <c:axId val="67440205"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50633389"/>
+        <c:axId val="37551409"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46297849"/>
+        <c:crossAx val="67440205"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2464,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46297849"/>
+        <c:axId val="67440205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2504,7 +2504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50633389"/>
+        <c:crossAx val="37551409"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Analise-Critica/Analise-Critica-modelo.xlsx
+++ b/Analise-Critica/Analise-Critica-modelo.xlsx
@@ -2194,11 +2194,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="48465311"/>
-        <c:axId val="80558773"/>
+        <c:axId val="57271520"/>
+        <c:axId val="26069386"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48465311"/>
+        <c:axId val="57271520"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2230,7 +2230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80558773"/>
+        <c:crossAx val="26069386"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2238,7 +2238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80558773"/>
+        <c:axId val="26069386"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2278,7 +2278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48465311"/>
+        <c:crossAx val="57271520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2420,11 +2420,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="37551409"/>
-        <c:axId val="67440205"/>
+        <c:axId val="18422225"/>
+        <c:axId val="86636209"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37551409"/>
+        <c:axId val="18422225"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67440205"/>
+        <c:crossAx val="86636209"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2464,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67440205"/>
+        <c:axId val="86636209"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2504,7 +2504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37551409"/>
+        <c:crossAx val="18422225"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5430,16 +5430,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H21" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Item da entrada: a, b, c1 a c7, d, e ou f" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C21" type="list">
       <formula1>"a,b,c1,c2,c3,c4,c5,c6,c7,d,e,f"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Melhoria, Mudança no sistema ou Recursos" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E7:E21" type="list">
       <formula1>"Melhoria,Mudança no sistema,Recursos"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H21" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J7:J21" type="decimal">

--- a/Analise-Critica/Analise-Critica-modelo.xlsx
+++ b/Analise-Critica/Analise-Critica-modelo.xlsx
@@ -1456,7 +1456,7 @@
     <t xml:space="preserve">Organismo de certificação</t>
   </si>
   <si>
-    <t xml:space="preserve">Visitar o cliente que concentra as reclamações e combinar um plano conjunto.</t>
+    <t xml:space="preserve">Fazer a segunda visita ao cliente A e rever o plano conjunto de outubro de 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">c2 · Objetivos da qualidade</t>
@@ -2194,11 +2194,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="57271520"/>
-        <c:axId val="26069386"/>
+        <c:axId val="54846932"/>
+        <c:axId val="24873935"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57271520"/>
+        <c:axId val="54846932"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2230,7 +2230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26069386"/>
+        <c:crossAx val="24873935"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2238,7 +2238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26069386"/>
+        <c:axId val="24873935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2278,7 +2278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57271520"/>
+        <c:crossAx val="54846932"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2420,11 +2420,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="18422225"/>
-        <c:axId val="86636209"/>
+        <c:axId val="27232066"/>
+        <c:axId val="8719270"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="18422225"/>
+        <c:axId val="27232066"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86636209"/>
+        <c:crossAx val="8719270"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2464,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86636209"/>
+        <c:axId val="8719270"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2504,7 +2504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18422225"/>
+        <c:crossAx val="27232066"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Analise-Critica/Analise-Critica-modelo.xlsx
+++ b/Analise-Critica/Analise-Critica-modelo.xlsx
@@ -1150,7 +1150,7 @@
     <t xml:space="preserve">Os objetivos do delivery foram alcançados. Manter.</t>
   </si>
   <si>
-    <t xml:space="preserve">63% dos elementos dos processos estão definidos. Quatro processos não têm indicador. O salão não tem padrão.</t>
+    <t xml:space="preserve">64% dos elementos dos processos estão definidos. Quatro processos não têm indicador. O salão não tem padrão.</t>
   </si>
   <si>
     <t xml:space="preserve">O sistema cobre bem o delivery, e pouco o restante da loja.</t>
@@ -1357,7 +1357,7 @@
     <t xml:space="preserve">Gerente de engenharia</t>
   </si>
   <si>
-    <t xml:space="preserve">Orçar os medidores de espessura em linha para as extrusoras 3 e 4.</t>
+    <t xml:space="preserve">Orçar os medidores de espessura em linha para as extrusoras 3 e 4 e levar a compra à aprovação.</t>
   </si>
   <si>
     <t xml:space="preserve">Orçamento recebido. Compra não aprovada.</t>
@@ -2194,11 +2194,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="54846932"/>
-        <c:axId val="24873935"/>
+        <c:axId val="34474347"/>
+        <c:axId val="16323352"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54846932"/>
+        <c:axId val="34474347"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2230,7 +2230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24873935"/>
+        <c:crossAx val="16323352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2238,7 +2238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24873935"/>
+        <c:axId val="16323352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2278,7 +2278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54846932"/>
+        <c:crossAx val="34474347"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2420,11 +2420,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="27232066"/>
-        <c:axId val="8719270"/>
+        <c:axId val="86632240"/>
+        <c:axId val="91887870"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27232066"/>
+        <c:axId val="86632240"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8719270"/>
+        <c:crossAx val="91887870"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2464,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8719270"/>
+        <c:axId val="91887870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2504,7 +2504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27232066"/>
+        <c:crossAx val="86632240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2589,7 +2589,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7400880" y="6324480"/>
+        <a:off x="7400880" y="6477120"/>
         <a:ext cx="6119640" cy="2015640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -7160,7 +7160,7 @@
         <v>Concluída no prazo</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="n">
         <v>7</v>
       </c>
